--- a/output/yearly_population_iteration_68_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_68_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4146</v>
+        <v>4293</v>
       </c>
       <c r="C2" t="n">
-        <v>10880</v>
+        <v>3965</v>
       </c>
       <c r="D2" t="n">
-        <v>22097</v>
+        <v>24995</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2592</v>
+        <v>2801</v>
       </c>
       <c r="C3" t="n">
-        <v>5067</v>
+        <v>5444</v>
       </c>
       <c r="D3" t="n">
-        <v>16306</v>
+        <v>14386</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2195</v>
+        <v>2293</v>
       </c>
       <c r="C4" t="n">
-        <v>5693</v>
+        <v>5768</v>
       </c>
       <c r="D4" t="n">
-        <v>8611</v>
+        <v>5987</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1485</v>
+        <v>1551</v>
       </c>
       <c r="C5" t="n">
-        <v>5412</v>
+        <v>4952</v>
       </c>
       <c r="D5" t="n">
-        <v>3126</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>848</v>
+        <v>925</v>
       </c>
       <c r="C6" t="n">
-        <v>3802</v>
+        <v>3439</v>
       </c>
       <c r="D6" t="n">
-        <v>1235</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>395</v>
+        <v>462</v>
       </c>
       <c r="C7" t="n">
-        <v>2092</v>
+        <v>2283</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C8" t="n">
-        <v>926</v>
+        <v>1138</v>
       </c>
       <c r="D8" t="n">
         <v>431</v>
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>364</v>
+        <v>461</v>
       </c>
       <c r="D9" t="n">
         <v>306</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -912,7 +912,7 @@
         <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4515</v>
+        <v>6657</v>
       </c>
       <c r="C2" t="n">
-        <v>8256</v>
+        <v>4380</v>
       </c>
       <c r="D2" t="n">
-        <v>24527</v>
+        <v>22051</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2684</v>
+        <v>2816</v>
       </c>
       <c r="C3" t="n">
-        <v>6745</v>
+        <v>4219</v>
       </c>
       <c r="D3" t="n">
-        <v>16154</v>
+        <v>14862</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>2150</v>
       </c>
       <c r="C4" t="n">
-        <v>5280</v>
+        <v>5440</v>
       </c>
       <c r="D4" t="n">
-        <v>9448</v>
+        <v>7175</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1580</v>
+        <v>1669</v>
       </c>
       <c r="C5" t="n">
-        <v>5374</v>
+        <v>5225</v>
       </c>
       <c r="D5" t="n">
-        <v>3873</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1015</v>
+        <v>1083</v>
       </c>
       <c r="C6" t="n">
-        <v>4476</v>
+        <v>4040</v>
       </c>
       <c r="D6" t="n">
-        <v>1478</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>527</v>
+        <v>589</v>
       </c>
       <c r="C7" t="n">
-        <v>2808</v>
+        <v>2791</v>
       </c>
       <c r="D7" t="n">
-        <v>733</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="C8" t="n">
-        <v>1416</v>
+        <v>1608</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C9" t="n">
-        <v>586</v>
+        <v>739</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>272</v>
+        <v>316</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5122</v>
+        <v>6568</v>
       </c>
       <c r="C2" t="n">
-        <v>9402</v>
+        <v>12554</v>
       </c>
       <c r="D2" t="n">
-        <v>27328</v>
+        <v>17690</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2777</v>
+        <v>3511</v>
       </c>
       <c r="C3" t="n">
-        <v>6532</v>
+        <v>3804</v>
       </c>
       <c r="D3" t="n">
-        <v>16124</v>
+        <v>14773</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1949</v>
+        <v>2084</v>
       </c>
       <c r="C4" t="n">
-        <v>5738</v>
+        <v>4747</v>
       </c>
       <c r="D4" t="n">
-        <v>10035</v>
+        <v>7994</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1584</v>
+        <v>1661</v>
       </c>
       <c r="C5" t="n">
-        <v>5171</v>
+        <v>5207</v>
       </c>
       <c r="D5" t="n">
-        <v>4558</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1124</v>
+        <v>1200</v>
       </c>
       <c r="C6" t="n">
-        <v>4798</v>
+        <v>4442</v>
       </c>
       <c r="D6" t="n">
-        <v>1766</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>640</v>
+        <v>704</v>
       </c>
       <c r="C7" t="n">
-        <v>3433</v>
+        <v>3264</v>
       </c>
       <c r="D7" t="n">
-        <v>827</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8">
@@ -1486,10 +1486,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>296</v>
+        <v>342</v>
       </c>
       <c r="C8" t="n">
-        <v>1933</v>
+        <v>2071</v>
       </c>
       <c r="D8" t="n">
         <v>479</v>
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="C9" t="n">
-        <v>894</v>
+        <v>1055</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>380</v>
+        <v>466</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4742</v>
+        <v>6039</v>
       </c>
       <c r="C2" t="n">
-        <v>6468</v>
+        <v>8536</v>
       </c>
       <c r="D2" t="n">
-        <v>22636</v>
+        <v>14861</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3387</v>
+        <v>3989</v>
       </c>
       <c r="C3" t="n">
-        <v>9747</v>
+        <v>7117</v>
       </c>
       <c r="D3" t="n">
-        <v>17787</v>
+        <v>15928</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1463</v>
+        <v>1534</v>
       </c>
       <c r="C4" t="n">
-        <v>8048</v>
+        <v>7596</v>
       </c>
       <c r="D4" t="n">
-        <v>9701</v>
+        <v>7495</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1038</v>
+        <v>1108</v>
       </c>
       <c r="C5" t="n">
-        <v>4702</v>
+        <v>4353</v>
       </c>
       <c r="D5" t="n">
-        <v>2955</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>591</v>
+        <v>650</v>
       </c>
       <c r="C6" t="n">
-        <v>3364</v>
+        <v>3198</v>
       </c>
       <c r="D6" t="n">
-        <v>810</v>
+        <v>749</v>
       </c>
     </row>
     <row r="7">
@@ -1783,10 +1783,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>316</v>
       </c>
       <c r="C7" t="n">
-        <v>1894</v>
+        <v>2029</v>
       </c>
       <c r="D7" t="n">
         <v>469</v>
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>876</v>
+        <v>1033</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>372</v>
+        <v>456</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2882</v>
+        <v>3722</v>
       </c>
       <c r="C2" t="n">
-        <v>2969</v>
+        <v>4733</v>
       </c>
       <c r="D2" t="n">
-        <v>16171</v>
+        <v>10561</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3450</v>
+        <v>4175</v>
       </c>
       <c r="C3" t="n">
-        <v>7598</v>
+        <v>7035</v>
       </c>
       <c r="D3" t="n">
-        <v>17592</v>
+        <v>14865</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1899</v>
+        <v>2135</v>
       </c>
       <c r="C4" t="n">
-        <v>8878</v>
+        <v>7436</v>
       </c>
       <c r="D4" t="n">
-        <v>10663</v>
+        <v>8706</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1133</v>
+        <v>1217</v>
       </c>
       <c r="C5" t="n">
-        <v>6179</v>
+        <v>5810</v>
       </c>
       <c r="D5" t="n">
-        <v>3792</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>701</v>
+        <v>765</v>
       </c>
       <c r="C6" t="n">
-        <v>3986</v>
+        <v>3792</v>
       </c>
       <c r="D6" t="n">
-        <v>1009</v>
+        <v>907</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>256</v>
+        <v>300</v>
       </c>
       <c r="C7" t="n">
-        <v>2449</v>
+        <v>2496</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>1158</v>
+        <v>1355</v>
       </c>
       <c r="D8" t="n">
         <v>335</v>
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>419</v>
+        <v>504</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2645</v>
+        <v>3047</v>
       </c>
       <c r="C2" t="n">
-        <v>11797</v>
+        <v>10778</v>
       </c>
       <c r="D2" t="n">
-        <v>12543</v>
+        <v>13698</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2702</v>
+        <v>3343</v>
       </c>
       <c r="C3" t="n">
-        <v>4858</v>
+        <v>5278</v>
       </c>
       <c r="D3" t="n">
-        <v>16216</v>
+        <v>13365</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2208</v>
+        <v>2603</v>
       </c>
       <c r="C4" t="n">
-        <v>8078</v>
+        <v>7085</v>
       </c>
       <c r="D4" t="n">
-        <v>11469</v>
+        <v>9446</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1295</v>
+        <v>1429</v>
       </c>
       <c r="C5" t="n">
-        <v>7294</v>
+        <v>6454</v>
       </c>
       <c r="D5" t="n">
-        <v>4732</v>
+        <v>3698</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>806</v>
+        <v>878</v>
       </c>
       <c r="C6" t="n">
-        <v>4955</v>
+        <v>4702</v>
       </c>
       <c r="D6" t="n">
-        <v>1396</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>430</v>
       </c>
       <c r="C7" t="n">
-        <v>3095</v>
+        <v>3078</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="C8" t="n">
-        <v>1687</v>
+        <v>1826</v>
       </c>
       <c r="D8" t="n">
         <v>354</v>
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>702</v>
+        <v>825</v>
       </c>
       <c r="D9" t="n">
         <v>263</v>
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>290</v>
+        <v>335</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2537,7 +2537,7 @@
         <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1584</v>
+        <v>1819</v>
       </c>
       <c r="C2" t="n">
-        <v>5606</v>
+        <v>5055</v>
       </c>
       <c r="D2" t="n">
-        <v>8785</v>
+        <v>9590</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2595</v>
+        <v>3156</v>
       </c>
       <c r="C3" t="n">
-        <v>6994</v>
+        <v>6965</v>
       </c>
       <c r="D3" t="n">
-        <v>15470</v>
+        <v>13100</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2431</v>
+        <v>2880</v>
       </c>
       <c r="C4" t="n">
-        <v>7665</v>
+        <v>7027</v>
       </c>
       <c r="D4" t="n">
-        <v>12126</v>
+        <v>9986</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1369</v>
+        <v>1510</v>
       </c>
       <c r="C5" t="n">
-        <v>8572</v>
+        <v>7550</v>
       </c>
       <c r="D5" t="n">
-        <v>4978</v>
+        <v>3913</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>668</v>
+        <v>754</v>
       </c>
       <c r="C6" t="n">
-        <v>5915</v>
+        <v>5714</v>
       </c>
       <c r="D6" t="n">
-        <v>1358</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>3189</v>
+        <v>3285</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1183</v>
+        <v>1363</v>
       </c>
       <c r="D8" t="n">
         <v>374</v>
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>284</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2834,7 +2834,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2161</v>
+        <v>2091</v>
       </c>
       <c r="C2" t="n">
-        <v>7226</v>
+        <v>4600</v>
       </c>
       <c r="D2" t="n">
-        <v>10831</v>
+        <v>10871</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1877</v>
+        <v>2209</v>
       </c>
       <c r="C3" t="n">
-        <v>5688</v>
+        <v>5405</v>
       </c>
       <c r="D3" t="n">
-        <v>13669</v>
+        <v>11742</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2186</v>
+        <v>2645</v>
       </c>
       <c r="C4" t="n">
-        <v>7196</v>
+        <v>6918</v>
       </c>
       <c r="D4" t="n">
-        <v>12271</v>
+        <v>10190</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1597</v>
+        <v>1832</v>
       </c>
       <c r="C5" t="n">
-        <v>8075</v>
+        <v>7229</v>
       </c>
       <c r="D5" t="n">
-        <v>5855</v>
+        <v>4764</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>848</v>
+        <v>955</v>
       </c>
       <c r="C6" t="n">
-        <v>7016</v>
+        <v>6492</v>
       </c>
       <c r="D6" t="n">
-        <v>1826</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>248</v>
+        <v>291</v>
       </c>
       <c r="C7" t="n">
-        <v>4318</v>
+        <v>4324</v>
       </c>
       <c r="D7" t="n">
-        <v>673</v>
+        <v>640</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1913</v>
+        <v>2086</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>574</v>
+        <v>672</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>46</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1473</v>
+        <v>1523</v>
       </c>
       <c r="C2" t="n">
-        <v>4053</v>
+        <v>3507</v>
       </c>
       <c r="D2" t="n">
-        <v>8750</v>
+        <v>8121</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1723</v>
+        <v>1902</v>
       </c>
       <c r="C3" t="n">
-        <v>5765</v>
+        <v>4613</v>
       </c>
       <c r="D3" t="n">
-        <v>12716</v>
+        <v>10998</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1916</v>
+        <v>2299</v>
       </c>
       <c r="C4" t="n">
-        <v>6590</v>
+        <v>6348</v>
       </c>
       <c r="D4" t="n">
-        <v>12190</v>
+        <v>10186</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1708</v>
+        <v>1991</v>
       </c>
       <c r="C5" t="n">
-        <v>7904</v>
+        <v>7242</v>
       </c>
       <c r="D5" t="n">
-        <v>6410</v>
+        <v>5335</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>981</v>
+        <v>1115</v>
       </c>
       <c r="C6" t="n">
-        <v>7628</v>
+        <v>6992</v>
       </c>
       <c r="D6" t="n">
-        <v>2205</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>223</v>
+        <v>272</v>
       </c>
       <c r="C7" t="n">
-        <v>5247</v>
+        <v>5150</v>
       </c>
       <c r="D7" t="n">
-        <v>754</v>
+        <v>721</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>2462</v>
+        <v>2646</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>657</v>
+        <v>784</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2615</v>
+        <v>2350</v>
       </c>
       <c r="C2" t="n">
-        <v>11694</v>
+        <v>9546</v>
       </c>
       <c r="D2" t="n">
-        <v>12432</v>
+        <v>7846</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1378</v>
+        <v>1487</v>
       </c>
       <c r="C3" t="n">
-        <v>4581</v>
+        <v>3742</v>
       </c>
       <c r="D3" t="n">
-        <v>11426</v>
+        <v>9948</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1607</v>
+        <v>1876</v>
       </c>
       <c r="C4" t="n">
-        <v>6112</v>
+        <v>5422</v>
       </c>
       <c r="D4" t="n">
-        <v>11895</v>
+        <v>9993</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1643</v>
+        <v>1935</v>
       </c>
       <c r="C5" t="n">
-        <v>7222</v>
+        <v>6722</v>
       </c>
       <c r="D5" t="n">
-        <v>6991</v>
+        <v>5824</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1135</v>
+        <v>1301</v>
       </c>
       <c r="C6" t="n">
-        <v>7668</v>
+        <v>7098</v>
       </c>
       <c r="D6" t="n">
-        <v>2701</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>401</v>
+        <v>487</v>
       </c>
       <c r="C7" t="n">
-        <v>6108</v>
+        <v>5833</v>
       </c>
       <c r="D7" t="n">
-        <v>916</v>
+        <v>852</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>3440</v>
+        <v>3528</v>
       </c>
       <c r="D8" t="n">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1222</v>
+        <v>1411</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>351</v>
+        <v>403</v>
       </c>
       <c r="D10" t="n">
         <v>185</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3739,7 +3739,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4464</v>
+        <v>5930</v>
       </c>
       <c r="C2" t="n">
-        <v>6719</v>
+        <v>11421</v>
       </c>
       <c r="D2" t="n">
-        <v>9458</v>
+        <v>11873</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1887</v>
+        <v>1681</v>
       </c>
       <c r="C2" t="n">
-        <v>6830</v>
+        <v>5422</v>
       </c>
       <c r="D2" t="n">
-        <v>9249</v>
+        <v>5774</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1917</v>
+        <v>2065</v>
       </c>
       <c r="C3" t="n">
-        <v>6527</v>
+        <v>5411</v>
       </c>
       <c r="D3" t="n">
-        <v>12464</v>
+        <v>10723</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2322</v>
+        <v>2741</v>
       </c>
       <c r="C4" t="n">
-        <v>8620</v>
+        <v>7665</v>
       </c>
       <c r="D4" t="n">
-        <v>12297</v>
+        <v>10319</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1079</v>
+        <v>1255</v>
       </c>
       <c r="C5" t="n">
-        <v>10662</v>
+        <v>9952</v>
       </c>
       <c r="D5" t="n">
-        <v>6383</v>
+        <v>5275</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>370</v>
+        <v>449</v>
       </c>
       <c r="C6" t="n">
-        <v>7413</v>
+        <v>7107</v>
       </c>
       <c r="D6" t="n">
-        <v>2078</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>3371</v>
+        <v>3457</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1197</v>
+        <v>1382</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>394</v>
       </c>
       <c r="D9" t="n">
         <v>181</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5842</v>
+        <v>6566</v>
       </c>
       <c r="C2" t="n">
-        <v>7681</v>
+        <v>7282</v>
       </c>
       <c r="D2" t="n">
-        <v>26876</v>
+        <v>11837</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1898</v>
+        <v>2519</v>
       </c>
       <c r="C3" t="n">
-        <v>3386</v>
+        <v>5756</v>
       </c>
       <c r="D3" t="n">
-        <v>2228</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4059</v>
+        <v>3922</v>
       </c>
       <c r="C2" t="n">
-        <v>9831</v>
+        <v>5700</v>
       </c>
       <c r="D2" t="n">
-        <v>19851</v>
+        <v>13879</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3175</v>
+        <v>3730</v>
       </c>
       <c r="C3" t="n">
-        <v>5016</v>
+        <v>5708</v>
       </c>
       <c r="D3" t="n">
-        <v>6204</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>859</v>
+        <v>1128</v>
       </c>
       <c r="C4" t="n">
-        <v>2027</v>
+        <v>3416</v>
       </c>
       <c r="D4" t="n">
-        <v>1630</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4758</v>
+        <v>4405</v>
       </c>
       <c r="C2" t="n">
-        <v>7080</v>
+        <v>7090</v>
       </c>
       <c r="D2" t="n">
-        <v>28100</v>
+        <v>13462</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2970</v>
+        <v>3158</v>
       </c>
       <c r="C3" t="n">
-        <v>6614</v>
+        <v>4937</v>
       </c>
       <c r="D3" t="n">
-        <v>7940</v>
+        <v>5281</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1713</v>
+        <v>2066</v>
       </c>
       <c r="C4" t="n">
-        <v>3677</v>
+        <v>4643</v>
       </c>
       <c r="D4" t="n">
-        <v>2458</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>405</v>
+        <v>514</v>
       </c>
       <c r="C5" t="n">
-        <v>1203</v>
+        <v>1966</v>
       </c>
       <c r="D5" t="n">
-        <v>1228</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>76</v>
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4812</v>
+        <v>4676</v>
       </c>
       <c r="C2" t="n">
-        <v>11259</v>
+        <v>6884</v>
       </c>
       <c r="D2" t="n">
-        <v>33388</v>
+        <v>17957</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3117</v>
+        <v>3109</v>
       </c>
       <c r="C3" t="n">
-        <v>5965</v>
+        <v>5261</v>
       </c>
       <c r="D3" t="n">
-        <v>10445</v>
+        <v>6152</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1966</v>
+        <v>2205</v>
       </c>
       <c r="C4" t="n">
-        <v>5179</v>
+        <v>4704</v>
       </c>
       <c r="D4" t="n">
-        <v>3383</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>870</v>
+        <v>1058</v>
       </c>
       <c r="C5" t="n">
-        <v>2460</v>
+        <v>3312</v>
       </c>
       <c r="D5" t="n">
-        <v>1391</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="C6" t="n">
-        <v>746</v>
+        <v>1127</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4607</v>
+        <v>5274</v>
       </c>
       <c r="C2" t="n">
-        <v>8529</v>
+        <v>11611</v>
       </c>
       <c r="D2" t="n">
-        <v>34671</v>
+        <v>30097</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2864</v>
+        <v>2814</v>
       </c>
       <c r="C3" t="n">
-        <v>7064</v>
+        <v>4989</v>
       </c>
       <c r="D3" t="n">
-        <v>12415</v>
+        <v>7068</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1577</v>
+        <v>1651</v>
       </c>
       <c r="C4" t="n">
-        <v>4546</v>
+        <v>4104</v>
       </c>
       <c r="D4" t="n">
-        <v>3986</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>732</v>
+        <v>847</v>
       </c>
       <c r="C5" t="n">
-        <v>2829</v>
+        <v>2942</v>
       </c>
       <c r="D5" t="n">
-        <v>1360</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>262</v>
+        <v>316</v>
       </c>
       <c r="C6" t="n">
-        <v>1067</v>
+        <v>1478</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>349</v>
+        <v>466</v>
       </c>
       <c r="D7" t="n">
         <v>514</v>
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>235</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4420</v>
+        <v>4118</v>
       </c>
       <c r="C2" t="n">
-        <v>5644</v>
+        <v>5624</v>
       </c>
       <c r="D2" t="n">
-        <v>29323</v>
+        <v>31617</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3087</v>
+        <v>3386</v>
       </c>
       <c r="C3" t="n">
-        <v>6807</v>
+        <v>7624</v>
       </c>
       <c r="D3" t="n">
-        <v>15240</v>
+        <v>10416</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1940</v>
+        <v>1935</v>
       </c>
       <c r="C4" t="n">
-        <v>5950</v>
+        <v>4553</v>
       </c>
       <c r="D4" t="n">
-        <v>5564</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1016</v>
+        <v>1116</v>
       </c>
       <c r="C5" t="n">
-        <v>3731</v>
+        <v>3561</v>
       </c>
       <c r="D5" t="n">
-        <v>1809</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>459</v>
+        <v>535</v>
       </c>
       <c r="C6" t="n">
-        <v>2051</v>
+        <v>2289</v>
       </c>
       <c r="D6" t="n">
-        <v>877</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="C7" t="n">
-        <v>749</v>
+        <v>1031</v>
       </c>
       <c r="D7" t="n">
         <v>552</v>
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>291</v>
+        <v>350</v>
       </c>
       <c r="D8" t="n">
         <v>385</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
         <v>236</v>
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3212</v>
+        <v>3767</v>
       </c>
       <c r="C2" t="n">
-        <v>6244</v>
+        <v>6793</v>
       </c>
       <c r="D2" t="n">
-        <v>23610</v>
+        <v>28525</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3064</v>
+        <v>3085</v>
       </c>
       <c r="C3" t="n">
-        <v>5363</v>
+        <v>5683</v>
       </c>
       <c r="D3" t="n">
-        <v>16396</v>
+        <v>13058</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2155</v>
+        <v>2287</v>
       </c>
       <c r="C4" t="n">
-        <v>6303</v>
+        <v>6124</v>
       </c>
       <c r="D4" t="n">
-        <v>7252</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1276</v>
+        <v>1331</v>
       </c>
       <c r="C5" t="n">
-        <v>4846</v>
+        <v>4029</v>
       </c>
       <c r="D5" t="n">
-        <v>2438</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>659</v>
+        <v>751</v>
       </c>
       <c r="C6" t="n">
-        <v>2898</v>
+        <v>2934</v>
       </c>
       <c r="D6" t="n">
-        <v>1017</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="C7" t="n">
-        <v>1404</v>
+        <v>1683</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>519</v>
+        <v>686</v>
       </c>
       <c r="D8" t="n">
         <v>405</v>
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
         <v>297</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">

--- a/output/yearly_population_iteration_68_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_68_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4293</v>
+        <v>4453</v>
       </c>
       <c r="C2" t="n">
-        <v>3965</v>
+        <v>4987</v>
       </c>
       <c r="D2" t="n">
-        <v>24995</v>
+        <v>23127</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2801</v>
+        <v>3234</v>
       </c>
       <c r="C3" t="n">
-        <v>5444</v>
+        <v>2880</v>
       </c>
       <c r="D3" t="n">
-        <v>14386</v>
+        <v>11886</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2293</v>
+        <v>2640</v>
       </c>
       <c r="C4" t="n">
-        <v>5768</v>
+        <v>3112</v>
       </c>
       <c r="D4" t="n">
-        <v>5987</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1551</v>
+        <v>1735</v>
       </c>
       <c r="C5" t="n">
-        <v>4952</v>
+        <v>3194</v>
       </c>
       <c r="D5" t="n">
-        <v>2257</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>925</v>
+        <v>985</v>
       </c>
       <c r="C6" t="n">
-        <v>3439</v>
+        <v>2802</v>
       </c>
       <c r="D6" t="n">
-        <v>1070</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="C7" t="n">
-        <v>2283</v>
+        <v>1610</v>
       </c>
       <c r="D7" t="n">
-        <v>651</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C8" t="n">
-        <v>1138</v>
+        <v>674</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -881,10 +881,10 @@
         <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>461</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6657</v>
+        <v>7239</v>
       </c>
       <c r="C2" t="n">
-        <v>4380</v>
+        <v>7029</v>
       </c>
       <c r="D2" t="n">
-        <v>22051</v>
+        <v>20306</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2816</v>
+        <v>3110</v>
       </c>
       <c r="C3" t="n">
-        <v>4219</v>
+        <v>3413</v>
       </c>
       <c r="D3" t="n">
-        <v>14862</v>
+        <v>12686</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2150</v>
+        <v>2494</v>
       </c>
       <c r="C4" t="n">
-        <v>5440</v>
+        <v>2929</v>
       </c>
       <c r="D4" t="n">
-        <v>7175</v>
+        <v>6722</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1669</v>
+        <v>1913</v>
       </c>
       <c r="C5" t="n">
-        <v>5225</v>
+        <v>3056</v>
       </c>
       <c r="D5" t="n">
-        <v>2739</v>
+        <v>2913</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1083</v>
+        <v>1203</v>
       </c>
       <c r="C6" t="n">
-        <v>4040</v>
+        <v>2961</v>
       </c>
       <c r="D6" t="n">
-        <v>1237</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>589</v>
+        <v>632</v>
       </c>
       <c r="C7" t="n">
-        <v>2791</v>
+        <v>2154</v>
       </c>
       <c r="D7" t="n">
-        <v>699</v>
+        <v>716</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="C8" t="n">
-        <v>1608</v>
+        <v>1104</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C9" t="n">
-        <v>739</v>
+        <v>467</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>316</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6568</v>
+        <v>7775</v>
       </c>
       <c r="C2" t="n">
-        <v>12554</v>
+        <v>5696</v>
       </c>
       <c r="D2" t="n">
-        <v>17690</v>
+        <v>18196</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3511</v>
+        <v>3937</v>
       </c>
       <c r="C3" t="n">
-        <v>3804</v>
+        <v>4426</v>
       </c>
       <c r="D3" t="n">
-        <v>14773</v>
+        <v>12869</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2084</v>
+        <v>2361</v>
       </c>
       <c r="C4" t="n">
-        <v>4747</v>
+        <v>3067</v>
       </c>
       <c r="D4" t="n">
-        <v>7994</v>
+        <v>7490</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1661</v>
+        <v>1945</v>
       </c>
       <c r="C5" t="n">
-        <v>5207</v>
+        <v>2933</v>
       </c>
       <c r="D5" t="n">
-        <v>3294</v>
+        <v>3381</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1200</v>
+        <v>1371</v>
       </c>
       <c r="C6" t="n">
-        <v>4442</v>
+        <v>2945</v>
       </c>
       <c r="D6" t="n">
-        <v>1410</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>704</v>
+        <v>785</v>
       </c>
       <c r="C7" t="n">
-        <v>3264</v>
+        <v>2509</v>
       </c>
       <c r="D7" t="n">
-        <v>765</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="C8" t="n">
-        <v>2071</v>
+        <v>1535</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C9" t="n">
-        <v>1055</v>
+        <v>729</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>466</v>
+        <v>331</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="D11" t="n">
         <v>204</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6039</v>
+        <v>6968</v>
       </c>
       <c r="C2" t="n">
-        <v>8536</v>
+        <v>3691</v>
       </c>
       <c r="D2" t="n">
-        <v>14861</v>
+        <v>14781</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3989</v>
+        <v>4627</v>
       </c>
       <c r="C3" t="n">
-        <v>7117</v>
+        <v>6263</v>
       </c>
       <c r="D3" t="n">
-        <v>15928</v>
+        <v>14286</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1534</v>
+        <v>1797</v>
       </c>
       <c r="C4" t="n">
-        <v>7596</v>
+        <v>4611</v>
       </c>
       <c r="D4" t="n">
-        <v>7495</v>
+        <v>7305</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1108</v>
+        <v>1266</v>
       </c>
       <c r="C5" t="n">
-        <v>4353</v>
+        <v>2886</v>
       </c>
       <c r="D5" t="n">
-        <v>2267</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>650</v>
+        <v>725</v>
       </c>
       <c r="C6" t="n">
-        <v>3198</v>
+        <v>2458</v>
       </c>
       <c r="D6" t="n">
-        <v>749</v>
+        <v>772</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>351</v>
       </c>
       <c r="C7" t="n">
-        <v>2029</v>
+        <v>1504</v>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C8" t="n">
-        <v>1033</v>
+        <v>714</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>456</v>
+        <v>324</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
         <v>199</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3722</v>
+        <v>4233</v>
       </c>
       <c r="C2" t="n">
-        <v>4733</v>
+        <v>1851</v>
       </c>
       <c r="D2" t="n">
-        <v>10561</v>
+        <v>11174</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4175</v>
+        <v>4880</v>
       </c>
       <c r="C3" t="n">
-        <v>7035</v>
+        <v>4510</v>
       </c>
       <c r="D3" t="n">
-        <v>14865</v>
+        <v>13511</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2135</v>
+        <v>2560</v>
       </c>
       <c r="C4" t="n">
-        <v>7436</v>
+        <v>5516</v>
       </c>
       <c r="D4" t="n">
-        <v>8706</v>
+        <v>8362</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1217</v>
+        <v>1411</v>
       </c>
       <c r="C5" t="n">
-        <v>5810</v>
+        <v>3726</v>
       </c>
       <c r="D5" t="n">
-        <v>2894</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>765</v>
+        <v>879</v>
       </c>
       <c r="C6" t="n">
-        <v>3792</v>
+        <v>2766</v>
       </c>
       <c r="D6" t="n">
-        <v>907</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="C7" t="n">
-        <v>2496</v>
+        <v>1901</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C8" t="n">
-        <v>1355</v>
+        <v>968</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>504</v>
+        <v>395</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3047</v>
+        <v>4666</v>
       </c>
       <c r="C2" t="n">
-        <v>10778</v>
+        <v>5977</v>
       </c>
       <c r="D2" t="n">
-        <v>13698</v>
+        <v>19399</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3343</v>
+        <v>3844</v>
       </c>
       <c r="C3" t="n">
-        <v>5278</v>
+        <v>2777</v>
       </c>
       <c r="D3" t="n">
-        <v>13365</v>
+        <v>12334</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2603</v>
+        <v>3136</v>
       </c>
       <c r="C4" t="n">
-        <v>7085</v>
+        <v>4870</v>
       </c>
       <c r="D4" t="n">
-        <v>9446</v>
+        <v>8917</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1429</v>
+        <v>1711</v>
       </c>
       <c r="C5" t="n">
-        <v>6454</v>
+        <v>4595</v>
       </c>
       <c r="D5" t="n">
-        <v>3698</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>878</v>
+        <v>1036</v>
       </c>
       <c r="C6" t="n">
-        <v>4702</v>
+        <v>3225</v>
       </c>
       <c r="D6" t="n">
-        <v>1181</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>430</v>
+        <v>498</v>
       </c>
       <c r="C7" t="n">
-        <v>3078</v>
+        <v>2298</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="C8" t="n">
-        <v>1826</v>
+        <v>1388</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>825</v>
+        <v>638</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>335</v>
+        <v>294</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1819</v>
+        <v>2686</v>
       </c>
       <c r="C2" t="n">
-        <v>5055</v>
+        <v>2597</v>
       </c>
       <c r="D2" t="n">
-        <v>9590</v>
+        <v>13220</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3156</v>
+        <v>3912</v>
       </c>
       <c r="C3" t="n">
-        <v>6965</v>
+        <v>3852</v>
       </c>
       <c r="D3" t="n">
-        <v>13100</v>
+        <v>12866</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2880</v>
+        <v>3497</v>
       </c>
       <c r="C4" t="n">
-        <v>7027</v>
+        <v>4472</v>
       </c>
       <c r="D4" t="n">
-        <v>9986</v>
+        <v>9434</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1510</v>
+        <v>1819</v>
       </c>
       <c r="C5" t="n">
-        <v>7550</v>
+        <v>5292</v>
       </c>
       <c r="D5" t="n">
-        <v>3913</v>
+        <v>4310</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>754</v>
+        <v>910</v>
       </c>
       <c r="C6" t="n">
-        <v>5714</v>
+        <v>4147</v>
       </c>
       <c r="D6" t="n">
-        <v>1167</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="C7" t="n">
-        <v>3285</v>
+        <v>2483</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1363</v>
+        <v>1101</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>328</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2091</v>
+        <v>4185</v>
       </c>
       <c r="C2" t="n">
-        <v>4600</v>
+        <v>6482</v>
       </c>
       <c r="D2" t="n">
-        <v>10871</v>
+        <v>16088</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2209</v>
+        <v>2845</v>
       </c>
       <c r="C3" t="n">
-        <v>5405</v>
+        <v>2859</v>
       </c>
       <c r="D3" t="n">
-        <v>11742</v>
+        <v>12031</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2645</v>
+        <v>3250</v>
       </c>
       <c r="C4" t="n">
-        <v>6918</v>
+        <v>4063</v>
       </c>
       <c r="D4" t="n">
-        <v>10190</v>
+        <v>9740</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1832</v>
+        <v>2254</v>
       </c>
       <c r="C5" t="n">
-        <v>7229</v>
+        <v>4831</v>
       </c>
       <c r="D5" t="n">
-        <v>4764</v>
+        <v>5056</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>955</v>
+        <v>1176</v>
       </c>
       <c r="C6" t="n">
-        <v>6492</v>
+        <v>4714</v>
       </c>
       <c r="D6" t="n">
-        <v>1520</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>369</v>
       </c>
       <c r="C7" t="n">
-        <v>4324</v>
+        <v>3223</v>
       </c>
       <c r="D7" t="n">
-        <v>640</v>
+        <v>695</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>2086</v>
+        <v>1688</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>672</v>
+        <v>583</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1523</v>
+        <v>2736</v>
       </c>
       <c r="C2" t="n">
-        <v>3507</v>
+        <v>4148</v>
       </c>
       <c r="D2" t="n">
-        <v>8121</v>
+        <v>11635</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1902</v>
+        <v>2905</v>
       </c>
       <c r="C3" t="n">
-        <v>4613</v>
+        <v>3995</v>
       </c>
       <c r="D3" t="n">
-        <v>10998</v>
+        <v>11876</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2299</v>
+        <v>2873</v>
       </c>
       <c r="C4" t="n">
-        <v>6348</v>
+        <v>3552</v>
       </c>
       <c r="D4" t="n">
-        <v>10186</v>
+        <v>9867</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1991</v>
+        <v>2469</v>
       </c>
       <c r="C5" t="n">
-        <v>7242</v>
+        <v>4606</v>
       </c>
       <c r="D5" t="n">
-        <v>5335</v>
+        <v>5583</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1115</v>
+        <v>1393</v>
       </c>
       <c r="C6" t="n">
-        <v>6992</v>
+        <v>4949</v>
       </c>
       <c r="D6" t="n">
-        <v>1811</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>385</v>
       </c>
       <c r="C7" t="n">
-        <v>5150</v>
+        <v>3866</v>
       </c>
       <c r="D7" t="n">
-        <v>721</v>
+        <v>781</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>2646</v>
+        <v>2159</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>784</v>
+        <v>737</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2350</v>
+        <v>5240</v>
       </c>
       <c r="C2" t="n">
-        <v>9546</v>
+        <v>7164</v>
       </c>
       <c r="D2" t="n">
-        <v>7846</v>
+        <v>10319</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1487</v>
+        <v>2385</v>
       </c>
       <c r="C3" t="n">
-        <v>3742</v>
+        <v>3581</v>
       </c>
       <c r="D3" t="n">
-        <v>9948</v>
+        <v>11159</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1876</v>
+        <v>2507</v>
       </c>
       <c r="C4" t="n">
-        <v>5422</v>
+        <v>3686</v>
       </c>
       <c r="D4" t="n">
-        <v>9993</v>
+        <v>9780</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1935</v>
+        <v>2411</v>
       </c>
       <c r="C5" t="n">
-        <v>6722</v>
+        <v>4078</v>
       </c>
       <c r="D5" t="n">
-        <v>5824</v>
+        <v>6071</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1301</v>
+        <v>1650</v>
       </c>
       <c r="C6" t="n">
-        <v>7098</v>
+        <v>4758</v>
       </c>
       <c r="D6" t="n">
-        <v>2209</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>487</v>
+        <v>668</v>
       </c>
       <c r="C7" t="n">
-        <v>5833</v>
+        <v>4310</v>
       </c>
       <c r="D7" t="n">
-        <v>852</v>
+        <v>944</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="C8" t="n">
-        <v>3528</v>
+        <v>2848</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>1411</v>
+        <v>1259</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5930</v>
+        <v>5332</v>
       </c>
       <c r="C2" t="n">
-        <v>11421</v>
+        <v>4255</v>
       </c>
       <c r="D2" t="n">
-        <v>11873</v>
+        <v>8247</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1681</v>
+        <v>3582</v>
       </c>
       <c r="C2" t="n">
-        <v>5422</v>
+        <v>3839</v>
       </c>
       <c r="D2" t="n">
-        <v>5774</v>
+        <v>7512</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2065</v>
+        <v>3387</v>
       </c>
       <c r="C3" t="n">
-        <v>5411</v>
+        <v>4813</v>
       </c>
       <c r="D3" t="n">
-        <v>10723</v>
+        <v>12018</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2741</v>
+        <v>3503</v>
       </c>
       <c r="C4" t="n">
-        <v>7665</v>
+        <v>5150</v>
       </c>
       <c r="D4" t="n">
-        <v>10319</v>
+        <v>10165</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1255</v>
+        <v>1658</v>
       </c>
       <c r="C5" t="n">
-        <v>9952</v>
+        <v>6362</v>
       </c>
       <c r="D5" t="n">
-        <v>5275</v>
+        <v>5696</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>449</v>
+        <v>617</v>
       </c>
       <c r="C6" t="n">
-        <v>7107</v>
+        <v>5342</v>
       </c>
       <c r="D6" t="n">
-        <v>1808</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="C7" t="n">
-        <v>3457</v>
+        <v>2791</v>
       </c>
       <c r="D7" t="n">
-        <v>537</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1382</v>
+        <v>1233</v>
       </c>
       <c r="D8" t="n">
-        <v>297</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6566</v>
+        <v>6252</v>
       </c>
       <c r="C2" t="n">
-        <v>7282</v>
+        <v>3070</v>
       </c>
       <c r="D2" t="n">
-        <v>11837</v>
+        <v>13831</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2519</v>
+        <v>2266</v>
       </c>
       <c r="C3" t="n">
-        <v>5756</v>
+        <v>2178</v>
       </c>
       <c r="D3" t="n">
-        <v>2633</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3922</v>
+        <v>4203</v>
       </c>
       <c r="C2" t="n">
-        <v>5700</v>
+        <v>9160</v>
       </c>
       <c r="D2" t="n">
-        <v>13879</v>
+        <v>18925</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3730</v>
+        <v>3496</v>
       </c>
       <c r="C3" t="n">
-        <v>5708</v>
+        <v>2317</v>
       </c>
       <c r="D3" t="n">
-        <v>3985</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1128</v>
+        <v>1018</v>
       </c>
       <c r="C4" t="n">
-        <v>3416</v>
+        <v>1340</v>
       </c>
       <c r="D4" t="n">
-        <v>1711</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4405</v>
+        <v>5033</v>
       </c>
       <c r="C2" t="n">
-        <v>7090</v>
+        <v>7021</v>
       </c>
       <c r="D2" t="n">
-        <v>13462</v>
+        <v>18072</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3158</v>
+        <v>3200</v>
       </c>
       <c r="C3" t="n">
-        <v>4937</v>
+        <v>5235</v>
       </c>
       <c r="D3" t="n">
-        <v>5281</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2066</v>
+        <v>1910</v>
       </c>
       <c r="C4" t="n">
-        <v>4643</v>
+        <v>1852</v>
       </c>
       <c r="D4" t="n">
-        <v>2095</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>514</v>
+        <v>478</v>
       </c>
       <c r="C5" t="n">
-        <v>1966</v>
+        <v>839</v>
       </c>
       <c r="D5" t="n">
-        <v>1243</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4676</v>
+        <v>5150</v>
       </c>
       <c r="C2" t="n">
-        <v>6884</v>
+        <v>4308</v>
       </c>
       <c r="D2" t="n">
-        <v>17957</v>
+        <v>20648</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3109</v>
+        <v>3337</v>
       </c>
       <c r="C3" t="n">
-        <v>5261</v>
+        <v>5362</v>
       </c>
       <c r="D3" t="n">
-        <v>6152</v>
+        <v>7404</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2205</v>
+        <v>2160</v>
       </c>
       <c r="C4" t="n">
-        <v>4704</v>
+        <v>3664</v>
       </c>
       <c r="D4" t="n">
-        <v>2612</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1058</v>
+        <v>995</v>
       </c>
       <c r="C5" t="n">
-        <v>3312</v>
+        <v>1356</v>
       </c>
       <c r="D5" t="n">
-        <v>1340</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>1127</v>
+        <v>569</v>
       </c>
       <c r="D6" t="n">
-        <v>953</v>
+        <v>940</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5274</v>
+        <v>5867</v>
       </c>
       <c r="C2" t="n">
-        <v>11611</v>
+        <v>3103</v>
       </c>
       <c r="D2" t="n">
-        <v>30097</v>
+        <v>19226</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2814</v>
+        <v>3083</v>
       </c>
       <c r="C3" t="n">
-        <v>4989</v>
+        <v>3939</v>
       </c>
       <c r="D3" t="n">
-        <v>7068</v>
+        <v>8369</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1651</v>
+        <v>1705</v>
       </c>
       <c r="C4" t="n">
-        <v>4104</v>
+        <v>3786</v>
       </c>
       <c r="D4" t="n">
-        <v>2770</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>847</v>
+        <v>835</v>
       </c>
       <c r="C5" t="n">
-        <v>2942</v>
+        <v>1878</v>
       </c>
       <c r="D5" t="n">
-        <v>1220</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="C6" t="n">
-        <v>1478</v>
+        <v>656</v>
       </c>
       <c r="D6" t="n">
-        <v>775</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>466</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
         <v>193</v>
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4118</v>
+        <v>5170</v>
       </c>
       <c r="C2" t="n">
-        <v>5624</v>
+        <v>4203</v>
       </c>
       <c r="D2" t="n">
-        <v>31617</v>
+        <v>20105</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3386</v>
+        <v>3742</v>
       </c>
       <c r="C3" t="n">
-        <v>7624</v>
+        <v>2937</v>
       </c>
       <c r="D3" t="n">
-        <v>10416</v>
+        <v>9650</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1935</v>
+        <v>2115</v>
       </c>
       <c r="C4" t="n">
-        <v>4553</v>
+        <v>3802</v>
       </c>
       <c r="D4" t="n">
-        <v>3525</v>
+        <v>4013</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1116</v>
+        <v>1133</v>
       </c>
       <c r="C5" t="n">
-        <v>3561</v>
+        <v>2992</v>
       </c>
       <c r="D5" t="n">
-        <v>1495</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="6">
@@ -6126,10 +6126,10 @@
         <v>535</v>
       </c>
       <c r="C6" t="n">
-        <v>2289</v>
+        <v>1363</v>
       </c>
       <c r="D6" t="n">
-        <v>849</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>1031</v>
+        <v>502</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>350</v>
+        <v>262</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6266,7 +6266,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3767</v>
+        <v>4106</v>
       </c>
       <c r="C2" t="n">
-        <v>6793</v>
+        <v>3465</v>
       </c>
       <c r="D2" t="n">
-        <v>28525</v>
+        <v>23482</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3085</v>
+        <v>3671</v>
       </c>
       <c r="C3" t="n">
-        <v>5683</v>
+        <v>3150</v>
       </c>
       <c r="D3" t="n">
-        <v>13058</v>
+        <v>10696</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2287</v>
+        <v>2544</v>
       </c>
       <c r="C4" t="n">
-        <v>6124</v>
+        <v>3216</v>
       </c>
       <c r="D4" t="n">
-        <v>4740</v>
+        <v>5027</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1331</v>
+        <v>1427</v>
       </c>
       <c r="C5" t="n">
-        <v>4029</v>
+        <v>3388</v>
       </c>
       <c r="D5" t="n">
-        <v>1805</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>751</v>
+        <v>769</v>
       </c>
       <c r="C6" t="n">
-        <v>2934</v>
+        <v>2224</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>945</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C7" t="n">
-        <v>1683</v>
+        <v>974</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>686</v>
+        <v>388</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>278</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_68_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_68_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4453</v>
+        <v>855</v>
       </c>
       <c r="C2" t="n">
-        <v>4987</v>
+        <v>2478</v>
       </c>
       <c r="D2" t="n">
-        <v>23127</v>
+        <v>16045</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3234</v>
+        <v>1452</v>
       </c>
       <c r="C3" t="n">
-        <v>2880</v>
+        <v>6426</v>
       </c>
       <c r="D3" t="n">
-        <v>11886</v>
+        <v>16577</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2640</v>
+        <v>1043</v>
       </c>
       <c r="C4" t="n">
-        <v>3112</v>
+        <v>7863</v>
       </c>
       <c r="D4" t="n">
-        <v>5859</v>
+        <v>7746</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1735</v>
+        <v>578</v>
       </c>
       <c r="C5" t="n">
-        <v>3194</v>
+        <v>4278</v>
       </c>
       <c r="D5" t="n">
-        <v>2457</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>985</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>2802</v>
+        <v>1504</v>
       </c>
       <c r="D6" t="n">
-        <v>1097</v>
+        <v>775</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>477</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>1610</v>
+        <v>577</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>185</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>674</v>
+        <v>337</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>39</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7239</v>
+        <v>1256</v>
       </c>
       <c r="C2" t="n">
-        <v>7029</v>
+        <v>6054</v>
       </c>
       <c r="D2" t="n">
-        <v>20306</v>
+        <v>19689</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3110</v>
+        <v>996</v>
       </c>
       <c r="C3" t="n">
-        <v>3413</v>
+        <v>3802</v>
       </c>
       <c r="D3" t="n">
-        <v>12686</v>
+        <v>15329</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2494</v>
+        <v>1075</v>
       </c>
       <c r="C4" t="n">
-        <v>2929</v>
+        <v>6913</v>
       </c>
       <c r="D4" t="n">
-        <v>6722</v>
+        <v>9121</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1913</v>
+        <v>702</v>
       </c>
       <c r="C5" t="n">
-        <v>3056</v>
+        <v>6122</v>
       </c>
       <c r="D5" t="n">
-        <v>2913</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1203</v>
+        <v>360</v>
       </c>
       <c r="C6" t="n">
-        <v>2961</v>
+        <v>2887</v>
       </c>
       <c r="D6" t="n">
-        <v>1304</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>632</v>
+        <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>2154</v>
+        <v>1027</v>
       </c>
       <c r="D7" t="n">
-        <v>716</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1104</v>
+        <v>448</v>
       </c>
       <c r="D8" t="n">
-        <v>467</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>467</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D10" t="n">
-        <v>257</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7775</v>
+        <v>670</v>
       </c>
       <c r="C2" t="n">
-        <v>5696</v>
+        <v>2514</v>
       </c>
       <c r="D2" t="n">
-        <v>18196</v>
+        <v>13264</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3937</v>
+        <v>1028</v>
       </c>
       <c r="C3" t="n">
-        <v>4426</v>
+        <v>4526</v>
       </c>
       <c r="D3" t="n">
-        <v>12869</v>
+        <v>15470</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2361</v>
+        <v>1174</v>
       </c>
       <c r="C4" t="n">
-        <v>3067</v>
+        <v>6274</v>
       </c>
       <c r="D4" t="n">
-        <v>7490</v>
+        <v>10084</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1945</v>
+        <v>720</v>
       </c>
       <c r="C5" t="n">
-        <v>2933</v>
+        <v>7030</v>
       </c>
       <c r="D5" t="n">
-        <v>3381</v>
+        <v>3668</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1371</v>
+        <v>299</v>
       </c>
       <c r="C6" t="n">
-        <v>2945</v>
+        <v>3806</v>
       </c>
       <c r="D6" t="n">
-        <v>1533</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>785</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2509</v>
+        <v>1015</v>
       </c>
       <c r="D7" t="n">
-        <v>788</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>380</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1535</v>
+        <v>463</v>
       </c>
       <c r="D8" t="n">
-        <v>498</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>729</v>
+        <v>240</v>
       </c>
       <c r="D9" t="n">
-        <v>335</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>331</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>263</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>168</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6968</v>
+        <v>723</v>
       </c>
       <c r="C2" t="n">
-        <v>3691</v>
+        <v>4367</v>
       </c>
       <c r="D2" t="n">
-        <v>14781</v>
+        <v>12125</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4627</v>
+        <v>737</v>
       </c>
       <c r="C3" t="n">
-        <v>6263</v>
+        <v>3081</v>
       </c>
       <c r="D3" t="n">
-        <v>14286</v>
+        <v>14194</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1797</v>
+        <v>985</v>
       </c>
       <c r="C4" t="n">
-        <v>4611</v>
+        <v>5280</v>
       </c>
       <c r="D4" t="n">
-        <v>7305</v>
+        <v>10708</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1266</v>
+        <v>825</v>
       </c>
       <c r="C5" t="n">
-        <v>2886</v>
+        <v>6573</v>
       </c>
       <c r="D5" t="n">
-        <v>2476</v>
+        <v>4603</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>725</v>
+        <v>430</v>
       </c>
       <c r="C6" t="n">
-        <v>2458</v>
+        <v>5358</v>
       </c>
       <c r="D6" t="n">
-        <v>772</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>1504</v>
+        <v>2265</v>
       </c>
       <c r="D7" t="n">
-        <v>488</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>714</v>
+        <v>693</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4233</v>
+        <v>485</v>
       </c>
       <c r="C2" t="n">
-        <v>1851</v>
+        <v>2185</v>
       </c>
       <c r="D2" t="n">
-        <v>11174</v>
+        <v>8767</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4880</v>
+        <v>639</v>
       </c>
       <c r="C3" t="n">
-        <v>4510</v>
+        <v>3290</v>
       </c>
       <c r="D3" t="n">
-        <v>13511</v>
+        <v>13095</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2560</v>
+        <v>824</v>
       </c>
       <c r="C4" t="n">
-        <v>5516</v>
+        <v>4287</v>
       </c>
       <c r="D4" t="n">
-        <v>8362</v>
+        <v>11020</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1411</v>
+        <v>860</v>
       </c>
       <c r="C5" t="n">
-        <v>3726</v>
+        <v>6142</v>
       </c>
       <c r="D5" t="n">
-        <v>3097</v>
+        <v>5371</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>879</v>
+        <v>519</v>
       </c>
       <c r="C6" t="n">
-        <v>2766</v>
+        <v>6073</v>
       </c>
       <c r="D6" t="n">
-        <v>965</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>341</v>
+        <v>151</v>
       </c>
       <c r="C7" t="n">
-        <v>1901</v>
+        <v>3328</v>
       </c>
       <c r="D7" t="n">
-        <v>531</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>968</v>
+        <v>1084</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4666</v>
+        <v>527</v>
       </c>
       <c r="C2" t="n">
-        <v>5977</v>
+        <v>4639</v>
       </c>
       <c r="D2" t="n">
-        <v>19399</v>
+        <v>9625</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3844</v>
+        <v>484</v>
       </c>
       <c r="C3" t="n">
-        <v>2777</v>
+        <v>2439</v>
       </c>
       <c r="D3" t="n">
-        <v>12334</v>
+        <v>11626</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3136</v>
+        <v>651</v>
       </c>
       <c r="C4" t="n">
-        <v>4870</v>
+        <v>3750</v>
       </c>
       <c r="D4" t="n">
-        <v>8917</v>
+        <v>11023</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1711</v>
+        <v>782</v>
       </c>
       <c r="C5" t="n">
-        <v>4595</v>
+        <v>5159</v>
       </c>
       <c r="D5" t="n">
-        <v>3912</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1036</v>
+        <v>607</v>
       </c>
       <c r="C6" t="n">
-        <v>3225</v>
+        <v>6045</v>
       </c>
       <c r="D6" t="n">
-        <v>1299</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>498</v>
+        <v>257</v>
       </c>
       <c r="C7" t="n">
-        <v>2298</v>
+        <v>4542</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>836</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>181</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1388</v>
+        <v>1995</v>
       </c>
       <c r="D8" t="n">
-        <v>370</v>
+        <v>505</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>638</v>
+        <v>670</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2686</v>
+        <v>354</v>
       </c>
       <c r="C2" t="n">
-        <v>2597</v>
+        <v>2412</v>
       </c>
       <c r="D2" t="n">
-        <v>13220</v>
+        <v>6931</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3912</v>
+        <v>657</v>
       </c>
       <c r="C3" t="n">
-        <v>3852</v>
+        <v>3242</v>
       </c>
       <c r="D3" t="n">
-        <v>12866</v>
+        <v>12460</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3497</v>
+        <v>1041</v>
       </c>
       <c r="C4" t="n">
-        <v>4472</v>
+        <v>5285</v>
       </c>
       <c r="D4" t="n">
-        <v>9434</v>
+        <v>11394</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1819</v>
+        <v>618</v>
       </c>
       <c r="C5" t="n">
-        <v>5292</v>
+        <v>8048</v>
       </c>
       <c r="D5" t="n">
-        <v>4310</v>
+        <v>5566</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>910</v>
+        <v>237</v>
       </c>
       <c r="C6" t="n">
-        <v>4147</v>
+        <v>5991</v>
       </c>
       <c r="D6" t="n">
-        <v>1280</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>167</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>2483</v>
+        <v>1955</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1101</v>
+        <v>656</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4185</v>
+        <v>180</v>
       </c>
       <c r="C2" t="n">
-        <v>6482</v>
+        <v>1554</v>
       </c>
       <c r="D2" t="n">
-        <v>16088</v>
+        <v>5314</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2845</v>
+        <v>447</v>
       </c>
       <c r="C3" t="n">
-        <v>2859</v>
+        <v>2496</v>
       </c>
       <c r="D3" t="n">
-        <v>12031</v>
+        <v>10770</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3250</v>
+        <v>717</v>
       </c>
       <c r="C4" t="n">
-        <v>4063</v>
+        <v>3976</v>
       </c>
       <c r="D4" t="n">
-        <v>9740</v>
+        <v>10776</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2254</v>
+        <v>571</v>
       </c>
       <c r="C5" t="n">
-        <v>4831</v>
+        <v>5975</v>
       </c>
       <c r="D5" t="n">
-        <v>5056</v>
+        <v>5719</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1176</v>
+        <v>229</v>
       </c>
       <c r="C6" t="n">
-        <v>4714</v>
+        <v>5713</v>
       </c>
       <c r="D6" t="n">
-        <v>1699</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>369</v>
+        <v>59</v>
       </c>
       <c r="C7" t="n">
-        <v>3223</v>
+        <v>2639</v>
       </c>
       <c r="D7" t="n">
-        <v>695</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1688</v>
+        <v>753</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>583</v>
+        <v>269</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>130</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>103</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2736</v>
+        <v>393</v>
       </c>
       <c r="C2" t="n">
-        <v>4148</v>
+        <v>12773</v>
       </c>
       <c r="D2" t="n">
-        <v>11635</v>
+        <v>14747</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2905</v>
+        <v>268</v>
       </c>
       <c r="C3" t="n">
-        <v>3995</v>
+        <v>1715</v>
       </c>
       <c r="D3" t="n">
-        <v>11876</v>
+        <v>9121</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2873</v>
+        <v>512</v>
       </c>
       <c r="C4" t="n">
-        <v>3552</v>
+        <v>3093</v>
       </c>
       <c r="D4" t="n">
-        <v>9867</v>
+        <v>10447</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2469</v>
+        <v>581</v>
       </c>
       <c r="C5" t="n">
-        <v>4606</v>
+        <v>4776</v>
       </c>
       <c r="D5" t="n">
-        <v>5583</v>
+        <v>6467</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1393</v>
+        <v>353</v>
       </c>
       <c r="C6" t="n">
-        <v>4949</v>
+        <v>5840</v>
       </c>
       <c r="D6" t="n">
-        <v>2033</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>385</v>
+        <v>119</v>
       </c>
       <c r="C7" t="n">
-        <v>3866</v>
+        <v>4174</v>
       </c>
       <c r="D7" t="n">
-        <v>781</v>
+        <v>841</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>2159</v>
+        <v>1665</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>737</v>
+        <v>492</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5240</v>
+        <v>665</v>
       </c>
       <c r="C2" t="n">
-        <v>7164</v>
+        <v>9969</v>
       </c>
       <c r="D2" t="n">
-        <v>10319</v>
+        <v>17537</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2385</v>
+        <v>267</v>
       </c>
       <c r="C3" t="n">
-        <v>3581</v>
+        <v>6275</v>
       </c>
       <c r="D3" t="n">
-        <v>11159</v>
+        <v>9303</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2507</v>
+        <v>351</v>
       </c>
       <c r="C4" t="n">
-        <v>3686</v>
+        <v>2314</v>
       </c>
       <c r="D4" t="n">
-        <v>9780</v>
+        <v>9799</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2411</v>
+        <v>504</v>
       </c>
       <c r="C5" t="n">
-        <v>4078</v>
+        <v>3836</v>
       </c>
       <c r="D5" t="n">
-        <v>6071</v>
+        <v>6958</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1650</v>
+        <v>419</v>
       </c>
       <c r="C6" t="n">
-        <v>4758</v>
+        <v>5268</v>
       </c>
       <c r="D6" t="n">
-        <v>2517</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>668</v>
+        <v>195</v>
       </c>
       <c r="C7" t="n">
-        <v>4310</v>
+        <v>4956</v>
       </c>
       <c r="D7" t="n">
-        <v>944</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>146</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>2848</v>
+        <v>2795</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1259</v>
+        <v>992</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>407</v>
+        <v>317</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>142</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5332</v>
+        <v>3786</v>
       </c>
       <c r="C2" t="n">
-        <v>4255</v>
+        <v>6565</v>
       </c>
       <c r="D2" t="n">
-        <v>8247</v>
+        <v>24709</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3582</v>
+        <v>606</v>
       </c>
       <c r="C2" t="n">
-        <v>3839</v>
+        <v>9694</v>
       </c>
       <c r="D2" t="n">
-        <v>7512</v>
+        <v>26660</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3387</v>
+        <v>352</v>
       </c>
       <c r="C3" t="n">
-        <v>4813</v>
+        <v>6980</v>
       </c>
       <c r="D3" t="n">
-        <v>12018</v>
+        <v>9797</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3503</v>
+        <v>275</v>
       </c>
       <c r="C4" t="n">
-        <v>5150</v>
+        <v>4129</v>
       </c>
       <c r="D4" t="n">
-        <v>10165</v>
+        <v>9420</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1658</v>
+        <v>405</v>
       </c>
       <c r="C5" t="n">
-        <v>6362</v>
+        <v>3032</v>
       </c>
       <c r="D5" t="n">
-        <v>5696</v>
+        <v>7116</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>617</v>
+        <v>424</v>
       </c>
       <c r="C6" t="n">
-        <v>5342</v>
+        <v>4585</v>
       </c>
       <c r="D6" t="n">
-        <v>2053</v>
+        <v>3766</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="C7" t="n">
-        <v>2791</v>
+        <v>5039</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>1233</v>
+        <v>3704</v>
       </c>
       <c r="D8" t="n">
-        <v>315</v>
+        <v>519</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>398</v>
+        <v>1716</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>571</v>
       </c>
       <c r="D10" t="n">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6252</v>
+        <v>3981</v>
       </c>
       <c r="C2" t="n">
-        <v>3070</v>
+        <v>6839</v>
       </c>
       <c r="D2" t="n">
-        <v>13831</v>
+        <v>29858</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2266</v>
+        <v>1222</v>
       </c>
       <c r="C3" t="n">
-        <v>2178</v>
+        <v>2592</v>
       </c>
       <c r="D3" t="n">
-        <v>2024</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4203</v>
+        <v>2472</v>
       </c>
       <c r="C2" t="n">
-        <v>9160</v>
+        <v>8687</v>
       </c>
       <c r="D2" t="n">
-        <v>18925</v>
+        <v>21941</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3496</v>
+        <v>2198</v>
       </c>
       <c r="C3" t="n">
-        <v>2317</v>
+        <v>4427</v>
       </c>
       <c r="D3" t="n">
-        <v>3858</v>
+        <v>8226</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1018</v>
+        <v>591</v>
       </c>
       <c r="C4" t="n">
-        <v>1340</v>
+        <v>1666</v>
       </c>
       <c r="D4" t="n">
-        <v>1589</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5033</v>
+        <v>1646</v>
       </c>
       <c r="C2" t="n">
-        <v>7021</v>
+        <v>5344</v>
       </c>
       <c r="D2" t="n">
-        <v>18072</v>
+        <v>26902</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3200</v>
+        <v>1927</v>
       </c>
       <c r="C3" t="n">
-        <v>5235</v>
+        <v>5923</v>
       </c>
       <c r="D3" t="n">
-        <v>5990</v>
+        <v>9924</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1910</v>
+        <v>1225</v>
       </c>
       <c r="C4" t="n">
-        <v>1852</v>
+        <v>3274</v>
       </c>
       <c r="D4" t="n">
-        <v>1976</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>478</v>
+        <v>299</v>
       </c>
       <c r="C5" t="n">
-        <v>839</v>
+        <v>1043</v>
       </c>
       <c r="D5" t="n">
-        <v>1212</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5150</v>
+        <v>1339</v>
       </c>
       <c r="C2" t="n">
-        <v>4308</v>
+        <v>4729</v>
       </c>
       <c r="D2" t="n">
-        <v>20648</v>
+        <v>23487</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3337</v>
+        <v>1482</v>
       </c>
       <c r="C3" t="n">
-        <v>5362</v>
+        <v>4853</v>
       </c>
       <c r="D3" t="n">
-        <v>7404</v>
+        <v>11925</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2160</v>
+        <v>1347</v>
       </c>
       <c r="C4" t="n">
-        <v>3664</v>
+        <v>4706</v>
       </c>
       <c r="D4" t="n">
-        <v>2629</v>
+        <v>4349</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>995</v>
+        <v>650</v>
       </c>
       <c r="C5" t="n">
-        <v>1356</v>
+        <v>2242</v>
       </c>
       <c r="D5" t="n">
-        <v>1314</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>271</v>
+        <v>184</v>
       </c>
       <c r="C6" t="n">
-        <v>569</v>
+        <v>669</v>
       </c>
       <c r="D6" t="n">
-        <v>940</v>
+        <v>852</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5867</v>
+        <v>1617</v>
       </c>
       <c r="C2" t="n">
-        <v>3103</v>
+        <v>10013</v>
       </c>
       <c r="D2" t="n">
-        <v>19226</v>
+        <v>33718</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3083</v>
+        <v>1172</v>
       </c>
       <c r="C3" t="n">
-        <v>3939</v>
+        <v>4168</v>
       </c>
       <c r="D3" t="n">
-        <v>8369</v>
+        <v>12842</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1705</v>
+        <v>1224</v>
       </c>
       <c r="C4" t="n">
-        <v>3786</v>
+        <v>4687</v>
       </c>
       <c r="D4" t="n">
-        <v>2961</v>
+        <v>5598</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>835</v>
+        <v>852</v>
       </c>
       <c r="C5" t="n">
-        <v>1878</v>
+        <v>3451</v>
       </c>
       <c r="D5" t="n">
-        <v>1227</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>301</v>
+        <v>362</v>
       </c>
       <c r="C6" t="n">
-        <v>656</v>
+        <v>1461</v>
       </c>
       <c r="D6" t="n">
-        <v>756</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>481</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5170</v>
+        <v>1804</v>
       </c>
       <c r="C2" t="n">
-        <v>4203</v>
+        <v>8686</v>
       </c>
       <c r="D2" t="n">
-        <v>20105</v>
+        <v>27979</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3742</v>
+        <v>1128</v>
       </c>
       <c r="C3" t="n">
-        <v>2937</v>
+        <v>6126</v>
       </c>
       <c r="D3" t="n">
-        <v>9650</v>
+        <v>14964</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2115</v>
+        <v>1044</v>
       </c>
       <c r="C4" t="n">
-        <v>3802</v>
+        <v>4325</v>
       </c>
       <c r="D4" t="n">
-        <v>4013</v>
+        <v>6679</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1133</v>
+        <v>902</v>
       </c>
       <c r="C5" t="n">
-        <v>2992</v>
+        <v>3984</v>
       </c>
       <c r="D5" t="n">
-        <v>1527</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="C6" t="n">
-        <v>1363</v>
+        <v>2367</v>
       </c>
       <c r="D6" t="n">
-        <v>840</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>502</v>
+        <v>941</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>262</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4106</v>
+        <v>1625</v>
       </c>
       <c r="C2" t="n">
-        <v>3465</v>
+        <v>5350</v>
       </c>
       <c r="D2" t="n">
-        <v>23482</v>
+        <v>21999</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3671</v>
+        <v>1667</v>
       </c>
       <c r="C3" t="n">
-        <v>3150</v>
+        <v>8932</v>
       </c>
       <c r="D3" t="n">
-        <v>10696</v>
+        <v>16609</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2544</v>
+        <v>833</v>
       </c>
       <c r="C4" t="n">
-        <v>3216</v>
+        <v>6523</v>
       </c>
       <c r="D4" t="n">
-        <v>5027</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1427</v>
+        <v>486</v>
       </c>
       <c r="C5" t="n">
-        <v>3388</v>
+        <v>2319</v>
       </c>
       <c r="D5" t="n">
-        <v>1957</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>769</v>
+        <v>188</v>
       </c>
       <c r="C6" t="n">
-        <v>2224</v>
+        <v>922</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>642</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>321</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>974</v>
+        <v>373</v>
       </c>
       <c r="D7" t="n">
-        <v>609</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>388</v>
+        <v>276</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
